--- a/Motor_Param.xlsx
+++ b/Motor_Param.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8fa820dbf13b2b2e/Escritorio/8vo Semestre/Sistemas de Control Automático 2/Git_PID/PID_Control_SCA2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C12B4B4-DE19-40FC-974C-A4044854BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{7C12B4B4-DE19-40FC-974C-A4044854BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46C25D61-6125-4B06-A3D1-9953D2C5DF18}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3505C609-621A-4D72-85AF-8C3EF7124E8D}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,6 +39,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={153150E6-C565-4DC9-ACC0-A7705D398430}</author>
+  </authors>
+  <commentList>
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{153150E6-C565-4DC9-ACC0-A7705D398430}">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Medido directamente entre los cables del devanado del motor </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
@@ -86,7 +105,7 @@
     <t>ω (Rad/s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Km </t>
+    <t xml:space="preserve">Km = Kt </t>
   </si>
 </sst>
 </file>
@@ -134,10 +153,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -153,6 +171,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Danis Gonzalez" id="{4D96F42A-2912-420B-B9B4-A1A61BEE031F}" userId="8fa820dbf13b2b2e" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -470,9 +494,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G4" dT="2026-05-07T19:15:37.45" personId="{4D96F42A-2912-420B-B9B4-A1A61BEE031F}" id="{153150E6-C565-4DC9-ACC0-A7705D398430}">
+    <text xml:space="preserve">Medido directamente entre los cables del devanado del motor </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E81A216-4E80-4B3C-9DF1-67AD088E19F0}">
-  <dimension ref="C2:I12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E81A216-4E80-4B3C-9DF1-67AD088E19F0}">
+  <dimension ref="C2:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
@@ -480,12 +512,12 @@
     <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>6</v>
       </c>
@@ -499,7 +531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4">
         <v>1</v>
       </c>
@@ -514,26 +546,26 @@
         <f>D4/E4</f>
         <v>35.753768844221113</v>
       </c>
-    </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="I7" s="2"/>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -553,7 +585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>1</v>
       </c>
@@ -578,5 +610,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Motor_Param.xlsx
+++ b/Motor_Param.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8fa820dbf13b2b2e/Escritorio/8vo Semestre/Sistemas de Control Automático 2/Git_PID/PID_Control_SCA2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{7C12B4B4-DE19-40FC-974C-A4044854BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46C25D61-6125-4B06-A3D1-9953D2C5DF18}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{7C12B4B4-DE19-40FC-974C-A4044854BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CAC1CE6-15FE-49B9-89DB-70B090A4407F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3505C609-621A-4D72-85AF-8C3EF7124E8D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Parámetros" sheetId="1" r:id="rId1"/>
+    <sheet name="Velocidad" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Resistencia de armadura</t>
   </si>
@@ -105,14 +105,47 @@
     <t>ω (Rad/s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Km = Kt </t>
+    <t>Tiempo (ms)</t>
+  </si>
+  <si>
+    <t>Velocidad (RPM)</t>
+  </si>
+  <si>
+    <t>Velocidad final (prom)</t>
+  </si>
+  <si>
+    <t>Punto del 63.2%</t>
+  </si>
+  <si>
+    <t>Tiempo para V(63.2%)</t>
+  </si>
+  <si>
+    <t>τm</t>
+  </si>
+  <si>
+    <t>Km = Kt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltaje aplicado = 6.07 V </t>
+  </si>
+  <si>
+    <t>Medición</t>
+  </si>
+  <si>
+    <t>Promed</t>
+  </si>
+  <si>
+    <t>Corriente en regimen permanente</t>
+  </si>
+  <si>
+    <t>Corriente en vacio [A]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,6 +157,17 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4E5B61"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4E5B61"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -153,9 +197,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -171,6 +224,1065 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PY"/>
+              <a:t>Velocidad (RPM) vs Tiempo (ms)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PY"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Velocidad!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Velocidad (RPM)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Velocidad!$C$4:$C$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>230</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Velocidad!$D$4:$D$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>171.43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>514.29</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>685.71</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>857.14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1028.57</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1114.29</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1285.71</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1285.71</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1285.71</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1371.43</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1457.14</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1371.43</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1457.14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1542.86</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1457.14</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1457.14</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1542.86</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1457.14</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1542.86</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1542.86</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1457.14</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1542.86</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1542.86</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EF13-42C1-9F83-8698803303E6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1420573200"/>
+        <c:axId val="1420572720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1420573200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1420572720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1420572720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1420573200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PY"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{945A9CBD-47A2-0A41-E9E0-17C63DE11076}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -504,20 +1616,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E81A216-4E80-4B3C-9DF1-67AD088E19F0}">
-  <dimension ref="C2:H12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C2:L22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:12">
       <c r="D2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:12">
       <c r="C3" t="s">
         <v>6</v>
       </c>
@@ -531,7 +1643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:12">
       <c r="C4">
         <v>1</v>
       </c>
@@ -549,23 +1661,36 @@
       <c r="G4">
         <v>17.8</v>
       </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="3:12">
       <c r="C5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="3:12">
       <c r="C6">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="3:12">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="3:12">
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="3:12">
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="3:12">
       <c r="E10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="3:12">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -582,10 +1707,11 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="3:12">
       <c r="C12">
         <v>1</v>
       </c>
@@ -606,10 +1732,329 @@
       <c r="H12" s="1">
         <f>(D12-F4*G12)/F12</f>
         <v>3.0765813247411511E-2</v>
+      </c>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="3:12">
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="3:12">
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="3:12" ht="16.5">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="3:12" ht="16.5">
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" ht="16.5">
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" ht="16.5">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <f>32/1000</f>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12">
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <f>31.7/1000</f>
+        <v>3.1699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:12">
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <f>30/1000</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12">
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <f>31.5/1000</f>
+        <v>3.15E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12">
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22">
+        <f>(D18+D19+D20+D21)/C21</f>
+        <v>3.1300000000000001E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DBFDDF1-B3B9-4F94-BDDC-D67571985089}">
+  <dimension ref="C2:I27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:8">
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="3:8">
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8">
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>171.43</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8">
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>514.29</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8">
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>685.71</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8">
+      <c r="C8">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>857.14</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8">
+      <c r="C9">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>1028.57</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8">
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10">
+        <v>1114.29</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8">
+      <c r="C11">
+        <v>70</v>
+      </c>
+      <c r="D11">
+        <v>1285.71</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8">
+      <c r="C12">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>1285.71</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8">
+      <c r="C13">
+        <v>90</v>
+      </c>
+      <c r="D13">
+        <v>1285.71</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8">
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>1371.43</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8">
+      <c r="C15">
+        <v>110</v>
+      </c>
+      <c r="D15">
+        <v>1457.14</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8">
+      <c r="C16">
+        <v>120</v>
+      </c>
+      <c r="D16">
+        <v>1371.43</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9">
+      <c r="C17">
+        <v>130</v>
+      </c>
+      <c r="D17">
+        <v>1457.14</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9">
+      <c r="C18">
+        <v>140</v>
+      </c>
+      <c r="D18">
+        <v>1542.86</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9">
+      <c r="C19">
+        <v>150</v>
+      </c>
+      <c r="D19">
+        <v>1457.14</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9">
+      <c r="C20">
+        <v>160</v>
+      </c>
+      <c r="D20">
+        <v>1457.14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20">
+        <f>(D17+D18+D19+D20+D21+D22+D23+D24+D25+D26+D27)/11</f>
+        <v>1503.8963636363637</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9">
+      <c r="C21">
+        <v>170</v>
+      </c>
+      <c r="D21">
+        <v>1542.86</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9">
+      <c r="C22">
+        <v>180</v>
+      </c>
+      <c r="D22">
+        <v>1457.14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22">
+        <f>0.632*I20</f>
+        <v>950.46250181818186</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9">
+      <c r="C23">
+        <v>190</v>
+      </c>
+      <c r="D23">
+        <v>1542.86</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9">
+      <c r="C24">
+        <v>200</v>
+      </c>
+      <c r="D24">
+        <v>1542.86</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24">
+        <f>C8+((I22-D8)/(D9-D8))*(C9-C8)</f>
+        <v>45.443767241333603</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9">
+      <c r="C25">
+        <v>210</v>
+      </c>
+      <c r="D25">
+        <v>1457.14</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9">
+      <c r="C26">
+        <v>220</v>
+      </c>
+      <c r="D26">
+        <v>1542.86</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26">
+        <f>I24/1000</f>
+        <v>4.5443767241333602E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9">
+      <c r="C27">
+        <v>230</v>
+      </c>
+      <c r="D27">
+        <v>1542.86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>